--- a/docs/excel-book/projets/Projet3-Gestion-de-stock.xlsx
+++ b/docs/excel-book/projets/Projet3-Gestion-de-stock.xlsx
@@ -871,11 +871,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49760706"/>
-        <c:axId val="99002019"/>
+        <c:axId val="14071030"/>
+        <c:axId val="70320823"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49760706"/>
+        <c:axId val="14071030"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -907,7 +907,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99002019"/>
+        <c:crossAx val="70320823"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -915,7 +915,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99002019"/>
+        <c:axId val="70320823"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -957,7 +957,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49760706"/>
+        <c:crossAx val="14071030"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
